--- a/experiment/test/results-Set5/Set5.xlsx
+++ b/experiment/test/results-Set5/Set5.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.83</v>
+        <v>35.67</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8951</v>
+        <v>0.9303</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.36</v>
+        <v>37.93</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9467</v>
+        <v>0.9701</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.31</v>
+        <v>31.33</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9265</v>
+        <v>0.9504</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.03</v>
+        <v>34.12</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7995</v>
+        <v>0.8365</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.96</v>
+        <v>33.03</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9176</v>
+        <v>0.9451000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.5</v>
+        <v>34.41</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8971</v>
+        <v>0.9265</v>
       </c>
     </row>
   </sheetData>

--- a/experiment/test/results-Set5/Set5.xlsx
+++ b/experiment/test/results-Set5/Set5.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.67</v>
+        <v>32.76</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9303</v>
+        <v>0.8782</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.93</v>
+        <v>31.32</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9701</v>
+        <v>0.8901</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.33</v>
+        <v>23.02</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9504</v>
+        <v>0.7472</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34.12</v>
+        <v>32.1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8365</v>
+        <v>0.7742</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.03</v>
+        <v>27.56</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.8515</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.41</v>
+        <v>29.35</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9265</v>
+        <v>0.8282</v>
       </c>
     </row>
   </sheetData>

--- a/experiment/test/results-Set5/Set5.xlsx
+++ b/experiment/test/results-Set5/Set5.xlsx
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.05</v>
+        <v>34.75</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9428</v>
+        <v>0.9419</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.85</v>
+        <v>28.51</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9206</v>
+        <v>0.9165</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.03</v>
+        <v>32.93</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.7967</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.73</v>
+        <v>30.63</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.28</v>
+        <v>32.11</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8941</v>
+        <v>0.8925</v>
       </c>
     </row>
   </sheetData>
